--- a/base/pacotes/arthen-arboris/preliminar-arthen-arboris.xlsx
+++ b/base/pacotes/arthen-arboris/preliminar-arthen-arboris.xlsx
@@ -645,7 +645,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 2026-04-14T07:43:50 | AC=12473 m² | UR=98 | padrão=medio-alto | 5 projetos similares de referência</t>
+          <t>Gerado em 2026-04-14T08:53:50 | AC=12473 m² | UR=98 | padrão=medio-alto | 5 projetos similares de referência</t>
         </is>
       </c>
     </row>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>6985741.908600001</v>
+        <v>5921422.5252</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>560.0700000000001</v>
+        <v>474.74</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1590845826539945</v>
+        <v>0.141770564257238</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>2</v>
@@ -733,16 +733,16 @@
         <v>155000</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.02218805132339383</v>
+        <v>0.02617614253000207</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=36)</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>367–1223</t>
+          <t>268–10661</t>
         </is>
       </c>
     </row>
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1644063.4938</v>
+        <v>1428405.6696</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>131.81</v>
+        <v>114.52</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.03743985366047639</v>
+        <v>0.03419885625550595</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>4</v>
@@ -771,16 +771,16 @@
         <v>24741.64</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.01504907814893055</v>
+        <v>0.01732115779611016</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=37)</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>83–176</t>
+          <t>41–3021</t>
         </is>
       </c>
     </row>
@@ -794,13 +794,13 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2461293.1434</v>
+        <v>2446450.2972</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>197.33</v>
+        <v>196.14</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.05605042350976258</v>
+        <v>0.0585728577187822</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>2</v>
@@ -809,16 +809,16 @@
         <v>32550.51</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.01322496269381189</v>
+        <v>0.01330519979794994</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=37)</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>100–313</t>
+          <t>96–5968</t>
         </is>
       </c>
     </row>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>8052306.428400001</v>
+        <v>8165062.167599999</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>645.58</v>
+        <v>654.62</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1833731941895937</v>
+        <v>0.1954877338629</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>18</v>
@@ -847,16 +847,16 @@
         <v>238512.2</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.02962035810743389</v>
+        <v>0.0292113146359677</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=36)</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>532–776</t>
+          <t>359–18029</t>
         </is>
       </c>
     </row>
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>1883419.98</v>
+        <v>1742475.306</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>151</v>
+        <v>139.7</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.04289066006169437</v>
+        <v>0.04171830439132188</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>12</v>
@@ -885,16 +885,16 @@
         <v>142371.53</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.0755920248865577</v>
+        <v>0.08170648359248542</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=33)</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>91–241</t>
+          <t>68–320</t>
         </is>
       </c>
     </row>
@@ -908,13 +908,13 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>710959.86</v>
+        <v>748378.7999999999</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.0161905140630237</v>
+        <v>0.01791766831409673</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>11</v>
@@ -923,16 +923,16 @@
         <v>590515.8199999999</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.8305895356736455</v>
+        <v>0.7890600588899632</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=33)</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>41–65</t>
+          <t>34–930</t>
         </is>
       </c>
     </row>
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>4070681.7528</v>
+        <v>4142526.1176</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>326.36</v>
+        <v>332.12</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.0927006345545336</v>
+        <v>0.09918026667463008</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>30</v>
@@ -961,16 +961,16 @@
         <v>1580080.26</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.3881610884744672</v>
+        <v>0.3814291606483413</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=33)</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>190–460</t>
+          <t>159–6126</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>2072136.1674</v>
+        <v>2152087.9692</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>166.13</v>
+        <v>172.54</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.04718824739105487</v>
+        <v>0.05152524151523748</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>30</v>
@@ -999,16 +999,16 @@
         <v>72310.94</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.03489680897309548</v>
+        <v>0.03360036440651648</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=35)</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>99–241</t>
+          <t>106–4373</t>
         </is>
       </c>
     </row>
@@ -1022,13 +1022,13 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>719316.7566</v>
+        <v>381548.4582</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>57.67</v>
+        <v>30.59</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.01638082361429082</v>
+        <v>0.009135024562136981</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>16</v>
@@ -1037,16 +1037,16 @@
         <v>75695.53999999999</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.1052325547896183</v>
+        <v>0.198390370536688</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=4)</t>
+          <t>calibrado (n=9)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>23–125</t>
+          <t>21–213</t>
         </is>
       </c>
     </row>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>924497.2776</v>
+        <v>756112.0475999999</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>74.12</v>
+        <v>60.62</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.02105334916405819</v>
+        <v>0.01810281755334239</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>5</v>
@@ -1075,16 +1075,16 @@
         <v>346137.59</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.3744062837032631</v>
+        <v>0.4577861060390278</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=8)</t>
+          <t>calibrado (n=15)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>45–228</t>
+          <t>41–2743</t>
         </is>
       </c>
     </row>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>805754.5079999999</v>
+        <v>749626.098</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>64.59999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.01834924927142686</v>
+        <v>0.01794753109462022</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>3</v>
@@ -1113,16 +1113,16 @@
         <v>182422.62</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.2263997510268972</v>
+        <v>0.2433514794731706</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=6)</t>
+          <t>calibrado (n=21)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>33–90</t>
+          <t>34–103</t>
         </is>
       </c>
     </row>
@@ -1136,13 +1136,13 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>2488234.7802</v>
+        <v>2482372.4796</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>199.49</v>
+        <v>199.02</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.05666395877951927</v>
+        <v>0.05943290579785884</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>8</v>
@@ -1151,16 +1151,16 @@
         <v>356539.36</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.1432900797131941</v>
+        <v>0.143628469510527</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=7)</t>
+          <t>calibrado (n=24)</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>160–246</t>
+          <t>113–269</t>
         </is>
       </c>
     </row>
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>1432646.4828</v>
+        <v>1553509.659</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>114.86</v>
+        <v>124.55</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.0326253060575246</v>
+        <v>0.03719409314201245</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>8</v>
@@ -1189,16 +1189,16 @@
         <v>557578.16</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.3891945198582804</v>
+        <v>0.3589151549652515</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=8)</t>
+          <t>calibrado (n=26)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>87–148</t>
+          <t>62–3983</t>
         </is>
       </c>
     </row>
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>4000583.6052</v>
+        <v>3757360.4952</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>320.74</v>
+        <v>301.24</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.09110430667674074</v>
+        <v>0.08995864004897496</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>30</v>
@@ -1227,16 +1227,16 @@
         <v>3313707.39</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.8283059965783014</v>
+        <v>0.8819242641831245</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=35)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>246–541</t>
+          <t>235–4673</t>
         </is>
       </c>
     </row>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>510768.531</v>
+        <v>745011.0954</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>40.95</v>
+        <v>59.73</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.01163160615580387</v>
+        <v>0.01783703880668329</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>27</v>
@@ -1265,16 +1265,16 @@
         <v>803895.15</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1.573893263208888</v>
+        <v>1.079037822340599</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=9)</t>
+          <t>calibrado (n=24)</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>26–148</t>
+          <t>24–1503</t>
         </is>
       </c>
     </row>
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1423790.667</v>
+        <v>1464078.3924</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>114.15</v>
+        <v>117.38</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.03242363474200274</v>
+        <v>0.03505293177847789</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>6</v>
@@ -1303,16 +1303,16 @@
         <v>398076.69</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.2795893379739369</v>
+        <v>0.2718957482511918</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=6)</t>
+          <t>calibrado (n=20)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>57–134</t>
+          <t>57–230</t>
         </is>
       </c>
     </row>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>2542492.2432</v>
+        <v>2507817.3588</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>203.84</v>
+        <v>201.06</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.05789955064222371</v>
+        <v>0.06004210652053813</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>30</v>
@@ -1341,16 +1341,16 @@
         <v>734054.09</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.2887143872172109</v>
+        <v>0.2927063597451321</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=7)</t>
+          <t>calibrado (n=27)</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>90–294</t>
+          <t>90–5321</t>
         </is>
       </c>
     </row>
@@ -1364,13 +1364,13 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>1183436.3424</v>
+        <v>623399.5403999999</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>94.88</v>
+        <v>49.98</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.02695010481227524</v>
+        <v>0.01492541770564257</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=3)</t>
+          <t>calibrado (n=15)</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>52–103</t>
+          <t>39–103</t>
         </is>
       </c>
     </row>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>43912123.92840001</v>
+        <v>41767644.477</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>3520.580000000001</v>
+        <v>3348.65</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>1</v>
@@ -1411,7 +1411,7 @@
         <v>9604189.49</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>0.218713845535231</v>
+        <v>0.2299432876874035</v>
       </c>
     </row>
     <row r="25">
@@ -1489,7 +1489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 4 refs): R$ 719.317  |  R$/m²: 57.67</t>
+          <t>Total calibrado V2 (mediana de 9 refs): R$ 381.548  |  R$/m²: 30.59</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>0.1052325589417065</v>
+        <v>0.1983903783644399</v>
       </c>
     </row>
   </sheetData>
@@ -2114,7 +2114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 8 refs): R$ 924.497  |  R$/m²: 74.12</t>
+          <t>Total calibrado V2 (mediana de 15 refs): R$ 756.112  |  R$/m²: 60.62</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>0.3744062834685409</v>
+        <v>0.4577861057520333</v>
       </c>
     </row>
   </sheetData>
@@ -2387,7 +2387,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 6 refs): R$ 805.755  |  R$/m²: 64.60</t>
+          <t>Total calibrado V2 (mediana de 21 refs): R$ 749.626  |  R$/m²: 60.10</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>0.2263997510268972</v>
+        <v>0.2433514794731706</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2596,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 7 refs): R$ 2.488.235  |  R$/m²: 199.49</t>
+          <t>Total calibrado V2 (mediana de 24 refs): R$ 2.482.372  |  R$/m²: 199.02</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>0.1432900806303102</v>
+        <v>0.1436284704298089</v>
       </c>
     </row>
   </sheetData>
@@ -2965,7 +2965,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 8 refs): R$ 1.432.646  |  R$/m²: 114.86</t>
+          <t>Total calibrado V2 (mediana de 26 refs): R$ 1.553.510  |  R$/m²: 124.55</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>0.3891945212672113</v>
+        <v>0.3589151562645675</v>
       </c>
     </row>
   </sheetData>
@@ -3334,7 +3334,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 4.000.584  |  R$/m²: 320.74</t>
+          <t>Total calibrado V2 (mediana de 35 refs): R$ 3.757.360  |  R$/m²: 301.24</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>0.8283059966297939</v>
+        <v>0.8819242642379501</v>
       </c>
     </row>
   </sheetData>
@@ -4407,7 +4407,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 9 refs): R$ 510.769  |  R$/m²: 40.95</t>
+          <t>Total calibrado V2 (mediana de 24 refs): R$ 745.011  |  R$/m²: 59.73</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="F34" s="27" t="n">
-        <v>1.573893260808583</v>
+        <v>1.079037820694986</v>
       </c>
     </row>
   </sheetData>
@@ -5384,7 +5384,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 6 refs): R$ 1.423.791  |  R$/m²: 114.15</t>
+          <t>Total calibrado V2 (mediana de 20 refs): R$ 1.464.078  |  R$/m²: 117.38</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>0.2795893407749104</v>
+        <v>0.2718957509750897</v>
       </c>
     </row>
   </sheetData>
@@ -5689,7 +5689,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 7 refs): R$ 2.542.492  |  R$/m²: 203.84</t>
+          <t>Total calibrado V2 (mediana de 27 refs): R$ 2.507.817  |  R$/m²: 201.06</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>0.2887143885385031</v>
+        <v>0.2927063610846935</v>
       </c>
     </row>
   </sheetData>
@@ -6642,7 +6642,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 3 refs): R$ 1.183.436  |  R$/m²: 94.88</t>
+          <t>Total calibrado V2 (mediana de 15 refs): R$ 623.400  |  R$/m²: 49.98</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 6.985.742  |  R$/m²: 560.07</t>
+          <t>Total calibrado V2 (mediana de 36 refs): R$ 5.921.423  |  R$/m²: 474.74</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>0.02218805132339383</v>
+        <v>0.02617614253000207</v>
       </c>
     </row>
   </sheetData>
@@ -7950,7 +7950,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 1.644.063  |  R$/m²: 131.81</t>
+          <t>Total calibrado V2 (mediana de 37 refs): R$ 1.428.406  |  R$/m²: 114.52</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>0.01504907835086923</v>
+        <v>0.01732115802853714</v>
       </c>
     </row>
   </sheetData>
@@ -8191,7 +8191,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 2.461.293  |  R$/m²: 197.33</t>
+          <t>Total calibrado V2 (mediana de 37 refs): R$ 2.446.450  |  R$/m²: 196.14</t>
         </is>
       </c>
     </row>
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>0.01322496350639287</v>
+        <v>0.01330520061546092</v>
       </c>
     </row>
   </sheetData>
@@ -8368,7 +8368,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 8.052.306  |  R$/m²: 645.58</t>
+          <t>Total calibrado V2 (mediana de 36 refs): R$ 8.165.062  |  R$/m²: 654.62</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>0.02962035869471904</v>
+        <v>0.02921131521514271</v>
       </c>
     </row>
   </sheetData>
@@ -9057,7 +9057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 1.883.420  |  R$/m²: 151.00</t>
+          <t>Total calibrado V2 (mediana de 33 refs): R$ 1.742.475  |  R$/m²: 139.70</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>0.07559202566891109</v>
+        <v>0.08170648443812152</v>
       </c>
     </row>
   </sheetData>
@@ -9554,7 +9554,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 710.960  |  R$/m²: 57.00</t>
+          <t>Total calibrado V2 (mediana de 33 refs): R$ 748.379  |  R$/m²: 60.00</t>
         </is>
       </c>
     </row>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>0.8305895416317876</v>
+        <v>0.7890600645501983</v>
       </c>
     </row>
   </sheetData>
@@ -10019,7 +10019,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 4.070.682  |  R$/m²: 326.36</t>
+          <t>Total calibrado V2 (mediana de 33 refs): R$ 4.142.526  |  R$/m²: 332.12</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>0.3881610887692581</v>
+        <v>0.3814291609380197</v>
       </c>
     </row>
   </sheetData>
@@ -11094,7 +11094,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 2.072.136  |  R$/m²: 166.13</t>
+          <t>Total calibrado V2 (mediana de 35 refs): R$ 2.152.088  |  R$/m²: 172.54</t>
         </is>
       </c>
     </row>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>0.03489680868595219</v>
+        <v>0.03360036413004079</v>
       </c>
     </row>
   </sheetData>
